--- a/src/data/opportunities_template.xlsx
+++ b/src/data/opportunities_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>Field</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Category *REQUIRED — must be one of the allowed values</t>
   </si>
   <si>
-    <t>Internship | Program | Full-Time &amp; Internship | Work Experience | Scholarship | Other</t>
+    <t>Internship | Graduate | Program | Part-Time | Full-Time | Scholarship | Others</t>
   </si>
   <si>
     <t>deadline</t>
@@ -150,6 +150,31 @@
   </si>
   <si>
     <t>https://www.atlassian.com/company/careers/all-jobs?team=Interns&amp;location=Australia%2CNew%20Zealand&amp;search=</t>
+  </si>
+  <si>
+    <t>Westpac Graduate Program</t>
+  </si>
+  <si>
+    <t>Westpac</t>
+  </si>
+  <si>
+    <t>/sponsors/current-sponsors/westpac.png</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>Westpac are looking for uncommon minds who expect to
+contribute from day one and have an impact. Their
+programs will get your career off to a flying start!
+If you’re curious, eager to learn and ready to explore what a
+career in banking could look like, this is a place where your
+ideas can grow - across areas like Financial Markets &amp;amp;
+Treasury, Corporate &amp;amp; Institutional Banking, Global
+Transaction Services and Group Treasury.</t>
+  </si>
+  <si>
+    <t>https://au.gradconnection.com/employers/westpac/jobs</t>
   </si>
 </sst>
 </file>
@@ -160,7 +185,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -185,6 +210,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -197,11 +227,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -213,7 +238,11 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF1F1F1F"/>
-      <name val="Docs-Roboto"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -248,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -264,6 +293,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -276,7 +308,7 @@
     <xf borderId="0" fillId="3" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -288,25 +320,25 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -645,6 +677,9 @@
         <v>28</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" s="5"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C10"/>
@@ -669,138 +704,138 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>1.0</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>46089.0</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="12">
         <v>1.0</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="13">
         <v>46068.0</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>3.0</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="15">
         <v>46142.0</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="18.0" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="5">
         <v>3.0</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="16" t="s">
@@ -810,14 +845,40 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="F6" s="18"/>
-      <c r="H6" s="19"/>
+    <row r="6" ht="127.5" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="18">
+        <v>46122.0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7">
-      <c r="C7" s="10"/>
+      <c r="C7" s="11"/>
       <c r="F7" s="18"/>
       <c r="H7" s="16"/>
+      <c r="I7" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -825,7 +886,8 @@
     <hyperlink r:id="rId2" ref="I3"/>
     <hyperlink r:id="rId3" ref="I4"/>
     <hyperlink r:id="rId4" ref="I5"/>
+    <hyperlink r:id="rId5" ref="I6"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>